--- a/artfynd/A 7976-2022 artfynd.xlsx
+++ b/artfynd/A 7976-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 7976-2022 artfynd.xlsx
+++ b/artfynd/A 7976-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112181676</v>
+        <v>112181761</v>
       </c>
       <c r="B2" t="n">
-        <v>78752</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,7 +714,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>654100</v>
+        <v>654104</v>
       </c>
       <c r="R2" t="n">
         <v>7183468</v>
@@ -789,16 +784,11 @@
         <v>112182359</v>
       </c>
       <c r="B3" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -833,7 +823,7 @@
         <v>654123</v>
       </c>
       <c r="R3" t="n">
-        <v>7183475</v>
+        <v>7183476</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,37 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112182647</v>
+        <v>112181676</v>
       </c>
       <c r="B4" t="n">
-        <v>78786</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -944,7 +929,7 @@
         <v>654100</v>
       </c>
       <c r="R4" t="n">
-        <v>7183467</v>
+        <v>7183468</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112181761</v>
+        <v>112181677</v>
       </c>
       <c r="B5" t="n">
-        <v>78753</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>654104</v>
+        <v>654095</v>
       </c>
       <c r="R5" t="n">
-        <v>7183468</v>
+        <v>7183643</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,37 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112181834</v>
+        <v>112182647</v>
       </c>
       <c r="B6" t="n">
-        <v>77442</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>654074</v>
+        <v>654100</v>
       </c>
       <c r="R6" t="n">
-        <v>7183511</v>
+        <v>7183467</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1227,6 +1202,112 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>112181834</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Rusfors, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>654075</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7183511</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-08-07</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-08-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7976-2022 artfynd.xlsx
+++ b/artfynd/A 7976-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112181761</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112182359</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112181676</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112181677</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112182647</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,8 +1338,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112181834</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>